--- a/reports/relatorio_investimento.xlsx
+++ b/reports/relatorio_investimento.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recomendações" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Momentum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liquidez" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volatilidade" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estatísticas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recomendações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Momentum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Liquidez" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Volatilidade" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Estatísticas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,76 +417,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>mom_retorno</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>mom_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>adtv_21</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amihud_medio_21</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>liquidez_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>vol_historica</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>vol_park_media</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>risco_score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mom_score_norm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>liq_score_norm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>risco_score_norm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>score_final</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>classificacao</t>
         </is>
@@ -507,48 +495,1824 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.106652823159147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.908838097726193</v>
+      </c>
+      <c r="D2" t="n">
+        <v>922750980.0244467</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.920102619817406e-11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>86.8421052631579</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3235244997262651</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.288088773789181</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36.84210526315789</v>
+      </c>
+      <c r="J2" t="n">
+        <v>97.36842105263158</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.8421052631579</v>
+      </c>
+      <c r="L2" t="n">
+        <v>63.15789473684211</v>
+      </c>
+      <c r="M2" t="n">
+        <v>83.94736842105263</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SBSP3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6626679346295958</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.600478917916642</v>
+      </c>
+      <c r="D3" t="n">
+        <v>441544818.0640811</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.205895207915079e-11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>73.68421052631579</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2590942379106599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2492847544911439</v>
+      </c>
+      <c r="I3" t="n">
+        <v>13.1578947368421</v>
+      </c>
+      <c r="J3" t="n">
+        <v>84.21052631578947</v>
+      </c>
+      <c r="K3" t="n">
+        <v>73.68421052631579</v>
+      </c>
+      <c r="L3" t="n">
+        <v>86.84210526315789</v>
+      </c>
+      <c r="M3" t="n">
+        <v>81.84210526315789</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7734146138262301</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.530344739530239</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1705996287.483052</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.075853233061011e-11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90.78947368421052</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3435419548285652</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2619657699356612</v>
+      </c>
+      <c r="I4" t="n">
+        <v>44.73684210526316</v>
+      </c>
+      <c r="J4" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="K4" t="n">
+        <v>90.78947368421052</v>
+      </c>
+      <c r="L4" t="n">
+        <v>55.26315789473684</v>
+      </c>
+      <c r="M4" t="n">
+        <v>81.71052631578947</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIVT3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6438363114776564</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.783950875130515</v>
+      </c>
+      <c r="D5" t="n">
+        <v>228389079.6364194</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.180471918170489e-11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56.57894736842105</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2537307087855292</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2597129424212162</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="J5" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="K5" t="n">
+        <v>56.57894736842105</v>
+      </c>
+      <c r="L5" t="n">
+        <v>94.73684210526316</v>
+      </c>
+      <c r="M5" t="n">
+        <v>81.18421052631579</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.826258701234609</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.34697203260651</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2504319366.731408</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.653206854744547e-12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96.05263157894737</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3584625556993587</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.244213702167613</v>
+      </c>
+      <c r="I6" t="n">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="J6" t="n">
+        <v>92.10526315789474</v>
+      </c>
+      <c r="K6" t="n">
+        <v>96.05263157894737</v>
+      </c>
+      <c r="L6" t="n">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="M6" t="n">
+        <v>79.86842105263159</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4309409104089377</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.023072130333396</v>
+      </c>
+      <c r="D7" t="n">
+        <v>448428780.712105</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.45808200797649e-11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77.63157894736841</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2590735884914634</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2239006783681077</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.52631578947368</v>
+      </c>
+      <c r="J7" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="K7" t="n">
+        <v>77.63157894736841</v>
+      </c>
+      <c r="L7" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="M7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EQTL3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4571715455526202</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.091621400783802</v>
+      </c>
+      <c r="D8" t="n">
+        <v>291770558.3168393</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.828616879305825e-11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63.1578947368421</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2670080933368929</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2185130074237583</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15.78947368421053</v>
+      </c>
+      <c r="J8" t="n">
+        <v>73.68421052631578</v>
+      </c>
+      <c r="K8" t="n">
+        <v>63.1578947368421</v>
+      </c>
+      <c r="L8" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="M8" t="n">
+        <v>73.68421052631578</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MULT3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6387592147127947</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.657536105629393</v>
+      </c>
+      <c r="D9" t="n">
+        <v>154305040.5853635</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.997018528393961e-11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>46.05263157894737</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.296308796920732</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2354155564636913</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26.31578947368421</v>
+      </c>
+      <c r="J9" t="n">
+        <v>86.8421052631579</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46.05263157894737</v>
+      </c>
+      <c r="L9" t="n">
+        <v>73.68421052631579</v>
+      </c>
+      <c r="M9" t="n">
+        <v>70.65789473684211</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FLRY3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7237475033668299</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.536386791838989</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56344854.29693858</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.443155496702113e-10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2580738007993148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.257038866247863</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.894736842105263</v>
+      </c>
+      <c r="J10" t="n">
+        <v>81.57894736842105</v>
+      </c>
+      <c r="K10" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="L10" t="n">
+        <v>92.10526315789474</v>
+      </c>
+      <c r="M10" t="n">
+        <v>69.73684210526316</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RENT3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8959167290423971</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.499253695683787</v>
+      </c>
+      <c r="D11" t="n">
+        <v>450171486.1635662</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.54684075854418e-11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3942189566309024</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3320110101092118</v>
+      </c>
+      <c r="I11" t="n">
+        <v>57.89473684210527</v>
+      </c>
+      <c r="J11" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="K11" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="L11" t="n">
+        <v>42.10526315789473</v>
+      </c>
+      <c r="M11" t="n">
+        <v>65.52631578947368</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4339930396778251</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.580710544414272</v>
+      </c>
+      <c r="D12" t="n">
+        <v>295708751.8895195</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.687104281561941e-11</v>
+      </c>
+      <c r="F12" t="n">
+        <v>63.15789473684211</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.271233694184451</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2343099934278734</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18.42105263157895</v>
+      </c>
+      <c r="J12" t="n">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="K12" t="n">
+        <v>63.15789473684211</v>
+      </c>
+      <c r="L12" t="n">
+        <v>81.57894736842105</v>
+      </c>
+      <c r="M12" t="n">
+        <v>64.47368421052632</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1647934233926287</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.675490181849865</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1736715529.943557</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.816597964091204e-12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>93.42105263157895</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2910985928738637</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2239248608749322</v>
+      </c>
+      <c r="I13" t="n">
+        <v>23.68421052631579</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28.94736842105263</v>
+      </c>
+      <c r="K13" t="n">
+        <v>93.42105263157895</v>
+      </c>
+      <c r="L13" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="M13" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7605294393585786</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.024279846777072</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28330991.32245382</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.254229160125709e-10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14.47368421052632</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2504282576228955</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3326078219009777</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.631578947368421</v>
+      </c>
+      <c r="J14" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14.47368421052632</v>
+      </c>
+      <c r="L14" t="n">
+        <v>97.36842105263158</v>
+      </c>
+      <c r="M14" t="n">
+        <v>61.97368421052632</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.983190379697093</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.029823207382221</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31884527.57791791</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.273324763354563e-10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14.47368421052632</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3537404966356666</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2855153525590515</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14.47368421052632</v>
+      </c>
+      <c r="L15" t="n">
+        <v>50</v>
+      </c>
+      <c r="M15" t="n">
+        <v>59.3421052631579</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.4550908820962751</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.231608789179409</v>
+      </c>
+      <c r="D16" t="n">
+        <v>192485912.6678694</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.807383855210085e-11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>53.94736842105264</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2819195261506808</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.293619242568309</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21.05263157894737</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="K16" t="n">
+        <v>53.94736842105264</v>
+      </c>
+      <c r="L16" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="M16" t="n">
+        <v>58.81578947368421</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6531998894740731</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.853233999223329</v>
+      </c>
+      <c r="D17" t="n">
+        <v>713702647.6791563</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.244420596447132e-11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4224094498614241</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3236871085515023</v>
+      </c>
+      <c r="I17" t="n">
+        <v>65.78947368421053</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57.89473684210527</v>
+      </c>
+      <c r="K17" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34.21052631578947</v>
+      </c>
+      <c r="M17" t="n">
+        <v>57.10526315789474</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.7456531693908959</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.948960769695831</v>
+      </c>
+      <c r="D18" t="n">
+        <v>153045213.5970978</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.039187500849517e-10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.42105263157895</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.341692369301025</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.300290147265702</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42.10526315789473</v>
+      </c>
+      <c r="J18" t="n">
+        <v>65.78947368421053</v>
+      </c>
+      <c r="K18" t="n">
+        <v>43.42105263157895</v>
+      </c>
+      <c r="L18" t="n">
+        <v>57.89473684210527</v>
+      </c>
+      <c r="M18" t="n">
+        <v>56.71052631578948</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.06382872317073374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.2410119623021368</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16120479357.74667</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8.255897656843548e-13</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="B19" t="n">
+        <v>0.03837827898130075</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.145021182985378</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15423015629.52241</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8.457422089777561e-13</v>
+      </c>
+      <c r="F19" t="n">
+        <v>98.68421052631578</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3124863125487505</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2257921486004191</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="J19" t="n">
+        <v>15.78947368421053</v>
+      </c>
+      <c r="K19" t="n">
+        <v>98.68421052631578</v>
+      </c>
+      <c r="L19" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="M19" t="n">
+        <v>56.44736842105263</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1354867965897566</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.49225460789873</v>
+      </c>
+      <c r="D20" t="n">
+        <v>490245443.254162</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.178613108252578e-11</v>
+      </c>
+      <c r="F20" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3330562355482519</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2396570599799558</v>
+      </c>
+      <c r="I20" t="n">
+        <v>39.47368421052632</v>
+      </c>
+      <c r="J20" t="n">
+        <v>21.05263157894737</v>
+      </c>
+      <c r="K20" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="L20" t="n">
+        <v>60.52631578947368</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50.26315789473684</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1763459967870189</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5913744860070599</v>
+      </c>
+      <c r="D21" t="n">
+        <v>420629894.1825322</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.932030399180212e-11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3217790633027844</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2985576973132138</v>
+      </c>
+      <c r="I21" t="n">
+        <v>34.21052631578947</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23.68421052631579</v>
+      </c>
+      <c r="K21" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="L21" t="n">
+        <v>65.78947368421052</v>
+      </c>
+      <c r="M21" t="n">
+        <v>49.73684210526315</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3492272064581818</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.021585900019255</v>
+      </c>
+      <c r="D22" t="n">
+        <v>696073326.609675</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.714924335729125e-11</v>
+      </c>
+      <c r="F22" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4388691765073899</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3263348037722833</v>
+      </c>
+      <c r="I22" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="J22" t="n">
+        <v>44.73684210526316</v>
+      </c>
+      <c r="K22" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="L22" t="n">
+        <v>28.94736842105263</v>
+      </c>
+      <c r="M22" t="n">
+        <v>49.47368421052632</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.01399596169859685</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.04772275458257268</v>
+      </c>
+      <c r="D23" t="n">
+        <v>943189969.6687971</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.091750202251135e-11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>86.84210526315789</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3474699481926735</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3075866317230015</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13.1578947368421</v>
+      </c>
+      <c r="K23" t="n">
+        <v>86.84210526315789</v>
+      </c>
+      <c r="L23" t="n">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="M23" t="n">
+        <v>47.10526315789474</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.535997061514274</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.94426424790819</v>
+      </c>
+      <c r="D24" t="n">
+        <v>175296868.8408806</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.78520624131512e-10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.42105263157895</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.4706666293881898</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3340341306832779</v>
+      </c>
+      <c r="I24" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="J24" t="n">
+        <v>63.1578947368421</v>
+      </c>
+      <c r="K24" t="n">
+        <v>43.42105263157895</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.68421052631578</v>
+      </c>
+      <c r="M24" t="n">
+        <v>45.39473684210526</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DASA3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.568862318620742</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.211536624651706</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4580358.51643199</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.871231443981652e-09</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.31578947368421</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.3747104398153134</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4808184373550535</v>
+      </c>
+      <c r="I25" t="n">
+        <v>55.26315789473685</v>
+      </c>
+      <c r="J25" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.31578947368421</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44.73684210526315</v>
+      </c>
+      <c r="M25" t="n">
+        <v>44.3421052631579</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.8647448826177111</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.909938083596433</v>
+      </c>
+      <c r="D26" t="n">
+        <v>76468728.68294489</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.921252436800111e-10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4446327289563209</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3747185935974208</v>
+      </c>
+      <c r="I26" t="n">
+        <v>73.68421052631578</v>
+      </c>
+      <c r="J26" t="n">
+        <v>60.52631578947368</v>
+      </c>
+      <c r="K26" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.31578947368422</v>
+      </c>
+      <c r="M26" t="n">
+        <v>41.57894736842106</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RAIL3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.07122382203184119</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.2097241698055382</v>
+      </c>
+      <c r="D27" t="n">
+        <v>176919738.2581893</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.636982463017525e-11</v>
+      </c>
+      <c r="F27" t="n">
         <v>50</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.3133365592592173</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.2328292850024383</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="G27" t="n">
+        <v>0.2995312287330881</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2978915632936899</v>
+      </c>
+      <c r="I27" t="n">
+        <v>28.94736842105263</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10.52631578947368</v>
+      </c>
+      <c r="K27" t="n">
+        <v>50</v>
+      </c>
+      <c r="L27" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="M27" t="n">
+        <v>40.52631578947368</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.2656681200182804</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9103290030260134</v>
+      </c>
+      <c r="D28" t="n">
+        <v>261717075.0633785</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.080768207794809e-11</v>
+      </c>
+      <c r="F28" t="n">
+        <v>59.21052631578948</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5345856019209829</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3748456130124284</v>
+      </c>
+      <c r="I28" t="n">
+        <v>81.57894736842105</v>
+      </c>
+      <c r="J28" t="n">
+        <v>42.10526315789473</v>
+      </c>
+      <c r="K28" t="n">
+        <v>59.21052631578948</v>
+      </c>
+      <c r="L28" t="n">
+        <v>18.42105263157895</v>
+      </c>
+      <c r="M28" t="n">
+        <v>40.13157894736842</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.4150599221888225</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.258453164102888</v>
+      </c>
+      <c r="D29" t="n">
+        <v>74514928.31536248</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.968594136450261e-10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>34.21052631578947</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.4369687611627522</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2687436700574962</v>
+      </c>
+      <c r="I29" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="J29" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" t="n">
+        <v>34.21052631578947</v>
+      </c>
+      <c r="L29" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="M29" t="n">
+        <v>39.73684210526316</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.5308602846180308</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8566437886696393</v>
+      </c>
+      <c r="D30" t="n">
+        <v>183974184.2333158</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.723421152102019e-10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6637809341492985</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5082301205932532</v>
+      </c>
+      <c r="I30" t="n">
+        <v>92.10526315789474</v>
+      </c>
+      <c r="J30" t="n">
+        <v>39.47368421052632</v>
+      </c>
+      <c r="K30" t="n">
+        <v>47.36842105263158</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.89473684210526</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32.36842105263158</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IRBR3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.2494697133749406</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7183642678685044</v>
+      </c>
+      <c r="D31" t="n">
+        <v>55163343.04733276</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.969762510434677e-10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>23.68421052631579</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4178949612441223</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3166634770852411</v>
+      </c>
+      <c r="I31" t="n">
+        <v>63.1578947368421</v>
+      </c>
+      <c r="J31" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="K31" t="n">
+        <v>23.68421052631579</v>
+      </c>
+      <c r="L31" t="n">
+        <v>36.8421052631579</v>
+      </c>
+      <c r="M31" t="n">
+        <v>30.78947368421053</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.1628721229641934</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.394639583289299</v>
+      </c>
+      <c r="D32" t="n">
+        <v>82458209.73131543</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.937981576896512e-10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.4174105868278621</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3614282511468484</v>
+      </c>
+      <c r="I32" t="n">
+        <v>60.52631578947368</v>
+      </c>
+      <c r="J32" t="n">
+        <v>18.42105263157895</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="L32" t="n">
+        <v>39.47368421052632</v>
+      </c>
+      <c r="M32" t="n">
+        <v>28.68421052631579</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.9179568765081674</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.753712723677596</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11432628.70494979</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.357181483926533e-09</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.263157894736844</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5609779632987553</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.460340290437876</v>
+      </c>
+      <c r="I33" t="n">
+        <v>86.8421052631579</v>
+      </c>
+      <c r="J33" t="n">
+        <v>55.26315789473685</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.263157894736844</v>
+      </c>
+      <c r="L33" t="n">
+        <v>13.1578947368421</v>
+      </c>
+      <c r="M33" t="n">
+        <v>27.63157894736842</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CVCB3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.4739883954925934</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8046118109737204</v>
+      </c>
+      <c r="D34" t="n">
+        <v>55144478.33412261</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5.403418634121958e-10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17.10526315789473</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5669545663473466</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5308910224744429</v>
+      </c>
+      <c r="I34" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.21052631578947</v>
+      </c>
+      <c r="K34" t="n">
+        <v>17.10526315789473</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10.52631578947368</v>
+      </c>
+      <c r="M34" t="n">
+        <v>21.97368421052632</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PCAR3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.5375494659659359</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8225441903496988</v>
+      </c>
+      <c r="D35" t="n">
+        <v>49254539.24626623</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.941707137775063e-10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11.8421052631579</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9763443508402192</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5549385993470599</v>
+      </c>
+      <c r="I35" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="J35" t="n">
+        <v>36.84210526315789</v>
+      </c>
+      <c r="K35" t="n">
+        <v>11.8421052631579</v>
+      </c>
+      <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>55</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NEUTRO</t>
+      <c r="M35" t="n">
+        <v>18.28947368421053</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    VENDA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.5955766083725074</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.9319662217702158</v>
+      </c>
+      <c r="D36" t="n">
+        <v>119817711.734413</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.587106578809253e-10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>35.52631578947368</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.500287577186058</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.451021941334785</v>
+      </c>
+      <c r="I36" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.631578947368421</v>
+      </c>
+      <c r="K36" t="n">
+        <v>35.52631578947368</v>
+      </c>
+      <c r="L36" t="n">
+        <v>21.05263157894737</v>
+      </c>
+      <c r="M36" t="n">
+        <v>18.02631578947368</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    VENDA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QUAL3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.3467642262769433</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6446726254956754</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12673054.83263958</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.417284433966897e-09</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.263157894736841</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8383327343305499</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6437572402229648</v>
+      </c>
+      <c r="I37" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="J37" t="n">
+        <v>26.31578947368421</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.263157894736841</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.26315789473685</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13.68421052631579</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    VENDA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SMTO3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.2308823202010385</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.5758503424359325</v>
+      </c>
+      <c r="D38" t="n">
+        <v>53942415.11683237</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.823713709167543e-10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>19.73684210526316</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5544748507893263</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4372923717065221</v>
+      </c>
+      <c r="I38" t="n">
+        <v>84.21052631578947</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="K38" t="n">
+        <v>19.73684210526316</v>
+      </c>
+      <c r="L38" t="n">
+        <v>15.78947368421053</v>
+      </c>
+      <c r="M38" t="n">
+        <v>12.76315789473684</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    VENDA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.1567912693856903</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.2566525952222988</v>
+      </c>
+      <c r="D39" t="n">
+        <v>56123705.31567619</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.756740487495644e-10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>18.42105263157895</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9327971659727921</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6176052380673689</v>
+      </c>
+      <c r="I39" t="n">
+        <v>97.36842105263158</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7.894736842105263</v>
+      </c>
+      <c r="K39" t="n">
+        <v>18.42105263157895</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.631578947368425</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9.473684210526315</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    VENDA FORTE</t>
         </is>
       </c>
     </row>
@@ -563,21 +2327,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>retorno_12m</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>momentum_score</t>
         </is>
@@ -586,14 +2350,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.983190379697093</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.029823207382221</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.106652823159147</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.908838097726193</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7734146138262301</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.530344739530239</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.826258701234609</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.34697203260651</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VIVT3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6438363114776564</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.783950875130515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MULT3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6387592147127947</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.657536105629393</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SBSP3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6626679346295958</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.600478917916642</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FLRY3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7237475033668299</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.536386791838989</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RENT3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8959167290423971</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.499253695683787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DASA3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.568862318620742</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.211536624651706</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EQTL3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4571715455526202</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.091621400783802</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7605294393585786</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.024279846777072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4309409104089377</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.023072130333396</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7456531693908959</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.948960769695831</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.535997061514274</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.94426424790819</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.8647448826177111</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.909938083596433</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6531998894740731</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.853233999223329</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9179568765081674</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.753712723677596</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4339930396778251</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.580710544414272</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4150599221888225</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.258453164102888</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.4550908820962751</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.231608789179409</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.3492272064581818</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.021585900019255</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.2656681200182804</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9103290030260134</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5308602846180308</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8566437886696393</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PCAR3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.5375494659659359</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8225441903496988</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CVCB3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.4739883954925934</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8046118109737204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IRBR3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.2494697133749406</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7183642678685044</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.1647934233926287</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.675490181849865</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QUAL3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.3467642262769433</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6446726254956754</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.1763459967870189</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5913744860070599</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.1354867965897566</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.49225460789873</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.1628721229641934</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.394639583289299</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.06382872317073374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.2410119623021368</v>
+      <c r="B34" t="n">
+        <v>0.03837827898130075</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.145021182985378</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.01399596169859685</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.04772275458257268</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RAIL3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.07122382203184119</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.2097241698055382</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.1567912693856903</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.2566525952222988</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SMTO3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.2308823202010385</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.5758503424359325</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.5955766083725074</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.9319662217702158</v>
       </c>
     </row>
   </sheetData>
@@ -607,26 +2852,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>adtv_21</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amihud_medio_21</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>liquidez_score</t>
         </is>
@@ -639,13 +2884,605 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16120479357.74667</v>
+        <v>15423015629.52241</v>
       </c>
       <c r="C2" t="n">
-        <v>8.255897656843548e-13</v>
+        <v>8.457422089777561e-13</v>
       </c>
       <c r="D2" t="n">
+        <v>98.68421052631578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2504319366.731408</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.653206854744547e-12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>96.05263157894737</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1736715529.943557</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7.816597964091204e-12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>93.42105263157895</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1705996287.483052</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.075853233061011e-11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>90.78947368421052</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>922750980.0244467</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.920102619817406e-11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.8421052631579</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>943189969.6687971</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.091750202251135e-11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>86.84210526315789</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>490245443.254162</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.178613108252578e-11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>78.94736842105263</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>713702647.6791563</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.244420596447132e-11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>78.94736842105263</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>448428780.712105</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.45808200797649e-11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>77.63157894736841</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>696073326.609675</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.714924335729125e-11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.31578947368422</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SBSP3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>441544818.0640811</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.205895207915079e-11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>73.68421052631579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RENT3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>450171486.1635662</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.54684075854418e-11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>71.05263157894737</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>420629894.1825322</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.932030399180212e-11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>68.42105263157895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>295708751.8895195</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.687104281561941e-11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>63.15789473684211</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EQTL3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>291770558.3168393</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.828616879305825e-11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>63.1578947368421</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>261717075.0633785</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.080768207794809e-11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>59.21052631578948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VIVT3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>228389079.6364194</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7.180471918170489e-11</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56.57894736842105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>192485912.6678694</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7.807383855210085e-11</v>
+      </c>
+      <c r="D19" t="n">
+        <v>53.94736842105264</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RAIL3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>176919738.2581893</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8.636982463017525e-11</v>
+      </c>
+      <c r="D20" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>183974184.2333158</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.723421152102019e-10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>47.36842105263158</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MULT3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>154305040.5853635</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9.997018528393961e-11</v>
+      </c>
+      <c r="D22" t="n">
+        <v>46.05263157894737</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>153045213.5970978</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.039187500849517e-10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>43.42105263157895</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>175296868.8408806</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.78520624131512e-10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>43.42105263157895</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>119817711.734413</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.587106578809253e-10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35.52631578947368</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>74514928.31536248</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.968594136450261e-10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>34.21052631578947</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>82458209.73131543</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.937981576896512e-10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>31.57894736842105</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>76468728.68294489</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.921252436800111e-10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.57894736842105</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FLRY3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>56344854.29693858</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.443155496702113e-10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>31.57894736842105</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IRBR3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>55163343.04733276</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.969762510434677e-10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23.68421052631579</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SMTO3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>53942415.11683237</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.823713709167543e-10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19.73684210526316</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>56123705.31567619</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.756740487495644e-10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18.42105263157895</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CVCB3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>55144478.33412261</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5.403418634121958e-10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17.10526315789473</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>31884527.57791791</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.273324763354563e-10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>14.47368421052632</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>28330991.32245382</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5.254229160125709e-10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.47368421052632</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PCAR3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>49254539.24626623</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9.941707137775063e-10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8421052631579</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>11432628.70494979</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.357181483926533e-09</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.263157894736844</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QUAL3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>12673054.83263958</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.417284433966897e-09</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5.263157894736841</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DASA3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4580358.51643199</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.871231443981652e-09</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.31578947368421</v>
       </c>
     </row>
   </sheetData>
@@ -659,26 +3496,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>vol_historica</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>vol_park_media</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>risco_score</t>
         </is>
@@ -687,16 +3524,608 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2504282576228955</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3326078219009777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.631578947368421</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIVT3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2537307087855292</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2597129424212162</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.263157894736842</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FLRY3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2580738007993148</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.257038866247863</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.894736842105263</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2590735884914634</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2239006783681077</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.52631578947368</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SBSP3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2590942379106599</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2492847544911439</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.1578947368421</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EQTL3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2670080933368929</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2185130074237583</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15.78947368421053</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.271233694184451</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2343099934278734</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18.42105263157895</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2819195261506808</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.293619242568309</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.05263157894737</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2910985928738637</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2239248608749322</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23.68421052631579</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MULT3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.296308796920732</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2354155564636913</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.31578947368421</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RAIL3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2995312287330881</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2978915632936899</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28.94736842105263</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.3133365592592173</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.2328292850024383</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B13" t="n">
+        <v>0.3124863125487505</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2257921486004191</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31.57894736842105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3217790633027844</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2985576973132138</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34.21052631578947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3235244997262651</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.288088773789181</v>
+      </c>
+      <c r="D15" t="n">
+        <v>36.84210526315789</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3330562355482519</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2396570599799558</v>
+      </c>
+      <c r="D16" t="n">
+        <v>39.47368421052632</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.341692369301025</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.300290147265702</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42.10526315789473</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3435419548285652</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2619657699356612</v>
+      </c>
+      <c r="D18" t="n">
+        <v>44.73684210526316</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.3474699481926735</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3075866317230015</v>
+      </c>
+      <c r="D19" t="n">
+        <v>47.36842105263158</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3537404966356666</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2855153525590515</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.3584625556993587</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.244213702167613</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52.63157894736842</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DASA3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3747104398153134</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.4808184373550535</v>
+      </c>
+      <c r="D22" t="n">
+        <v>55.26315789473685</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RENT3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.3942189566309024</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.3320110101092118</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57.89473684210527</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.4174105868278621</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3614282511468484</v>
+      </c>
+      <c r="D24" t="n">
+        <v>60.52631578947368</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IRBR3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.4178949612441223</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3166634770852411</v>
+      </c>
+      <c r="D25" t="n">
+        <v>63.1578947368421</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.4224094498614241</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.3236871085515023</v>
+      </c>
+      <c r="D26" t="n">
+        <v>65.78947368421053</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.4369687611627522</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2687436700574962</v>
+      </c>
+      <c r="D27" t="n">
+        <v>68.42105263157895</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.4388691765073899</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.3263348037722833</v>
+      </c>
+      <c r="D28" t="n">
+        <v>71.05263157894737</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.4446327289563209</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.3747185935974208</v>
+      </c>
+      <c r="D29" t="n">
+        <v>73.68421052631578</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.4706666293881898</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.3340341306832779</v>
+      </c>
+      <c r="D30" t="n">
+        <v>76.31578947368422</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.500287577186058</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.451021941334785</v>
+      </c>
+      <c r="D31" t="n">
+        <v>78.94736842105263</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.5345856019209829</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.3748456130124284</v>
+      </c>
+      <c r="D32" t="n">
+        <v>81.57894736842105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SMTO3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.5544748507893263</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4372923717065221</v>
+      </c>
+      <c r="D33" t="n">
+        <v>84.21052631578947</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.5609779632987553</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.460340290437876</v>
+      </c>
+      <c r="D34" t="n">
+        <v>86.8421052631579</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CVCB3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.5669545663473466</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5308910224744429</v>
+      </c>
+      <c r="D35" t="n">
+        <v>89.47368421052632</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.6637809341492985</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5082301205932532</v>
+      </c>
+      <c r="D36" t="n">
+        <v>92.10526315789474</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QUAL3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.8383327343305499</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6437572402229648</v>
+      </c>
+      <c r="D37" t="n">
+        <v>94.73684210526315</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.9327971659727921</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6176052380673689</v>
+      </c>
+      <c r="D38" t="n">
+        <v>97.36842105263158</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PCAR3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.9763443508402192</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5549385993470599</v>
+      </c>
+      <c r="D39" t="n">
         <v>100</v>
       </c>
     </row>
@@ -715,12 +4144,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -734,7 +4163,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>49.62%</t>
         </is>
       </c>
     </row>
@@ -746,7 +4175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R$ 16120.5M</t>
+          <t>R$ 783.6M</t>
         </is>
       </c>
     </row>
@@ -758,7 +4187,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.33%</t>
+          <t>42.03%</t>
         </is>
       </c>
     </row>
@@ -769,7 +4198,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -780,7 +4209,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-06 10:25</t>
+          <t>2026-03-06 13:14</t>
         </is>
       </c>
     </row>

--- a/reports/relatorio_investimento.xlsx
+++ b/reports/relatorio_investimento.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,37 +514,37 @@
         <v>0.9977540622750996</v>
       </c>
       <c r="C2" t="n">
-        <v>3.524412195831653</v>
+        <v>3.523123972571357</v>
       </c>
       <c r="D2" t="n">
-        <v>912551371.7137746</v>
+        <v>936702989.6828333</v>
       </c>
       <c r="E2" t="n">
-        <v>1.777495030877855e-11</v>
+        <v>1.602628234031397e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>35.71428571428571</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3070159486932991</v>
+        <v>0.3082365131172478</v>
       </c>
       <c r="H2" t="n">
         <v>0.2864134091531322</v>
       </c>
       <c r="I2" t="n">
-        <v>57.14285714285714</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>35.71428571428571</v>
+        <v>80</v>
       </c>
       <c r="L2" t="n">
-        <v>42.85714285714286</v>
+        <v>55</v>
       </c>
       <c r="M2" t="n">
-        <v>63.57142857142857</v>
+        <v>78.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -555,44 +555,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8207620043812851</v>
+        <v>0.7674675202273207</v>
       </c>
       <c r="C3" t="n">
-        <v>3.326412780089652</v>
+        <v>3.430425306946491</v>
       </c>
       <c r="D3" t="n">
-        <v>2398868387.076423</v>
+        <v>55593558.19838388</v>
       </c>
       <c r="E3" t="n">
-        <v>7.647041598128165e-12</v>
+        <v>2.730831357123434e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>78.57142857142857</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3567095385327261</v>
+        <v>0.01860445309896535</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2543366296571614</v>
+        <v>0.02885617245514972</v>
       </c>
       <c r="I3" t="n">
-        <v>85.71428571428571</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>85.71428571428571</v>
+        <v>90</v>
       </c>
       <c r="K3" t="n">
-        <v>78.57142857142857</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>14.28571428571429</v>
+        <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>62.14285714285714</v>
+        <v>75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -603,48 +603,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.002795726117860386</v>
+        <v>0.8207620043812851</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01056761352176577</v>
+        <v>3.315576634856987</v>
       </c>
       <c r="D4" t="n">
-        <v>14768618124.3547</v>
+        <v>2462520192.389824</v>
       </c>
       <c r="E4" t="n">
-        <v>7.794816665266045e-13</v>
+        <v>7.219603890928269e-12</v>
       </c>
       <c r="F4" t="n">
-        <v>92.85714285714286</v>
+        <v>97.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2541466886367213</v>
+        <v>0.3639053817002734</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2151546327929952</v>
+        <v>0.2579701008656878</v>
       </c>
       <c r="I4" t="n">
-        <v>14.28571428571428</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>14.28571428571428</v>
+        <v>85</v>
       </c>
       <c r="K4" t="n">
-        <v>92.85714285714286</v>
+        <v>97.5</v>
       </c>
       <c r="L4" t="n">
-        <v>85.71428571428572</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>59.28571428571428</v>
+        <v>73.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>COMPRA MODERADA</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,41 @@
         <v>0.6897098437509033</v>
       </c>
       <c r="C5" t="n">
-        <v>3.147924644483759</v>
+        <v>3.142741731706303</v>
       </c>
       <c r="D5" t="n">
-        <v>1686611723.969523</v>
+        <v>1720748464.992015</v>
       </c>
       <c r="E5" t="n">
-        <v>1.00673188090829e-11</v>
+        <v>9.931335673099017e-12</v>
       </c>
       <c r="F5" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3283468072948462</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2524664077859532</v>
+      </c>
+      <c r="I5" t="n">
         <v>50</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.3252733872921393</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2523599946119469</v>
-      </c>
-      <c r="I5" t="n">
-        <v>71.42857142857143</v>
-      </c>
       <c r="J5" t="n">
-        <v>71.42857142857143</v>
+        <v>80</v>
       </c>
       <c r="K5" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="L5" t="n">
         <v>50</v>
       </c>
-      <c r="L5" t="n">
-        <v>28.57142857142857</v>
-      </c>
       <c r="M5" t="n">
-        <v>52.14285714285714</v>
+        <v>73.25</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>COMPRA MODERADA</t>
         </is>
       </c>
     </row>
@@ -706,41 +706,41 @@
         <v>0.3611223549013032</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694658525640141</v>
+        <v>1.69311549253637</v>
       </c>
       <c r="D6" t="n">
-        <v>444647890.4039565</v>
+        <v>451478543.6449369</v>
       </c>
       <c r="E6" t="n">
-        <v>2.519363398876523e-11</v>
+        <v>2.610922385939225e-11</v>
       </c>
       <c r="F6" t="n">
-        <v>14.28571428571429</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>0.260145169409522</v>
+        <v>0.2621068729596222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2301036255099778</v>
+        <v>0.2309923257263864</v>
       </c>
       <c r="I6" t="n">
-        <v>28.57142857142857</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>57.14285714285714</v>
+        <v>65</v>
       </c>
       <c r="K6" t="n">
-        <v>14.28571428571429</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>71.42857142857143</v>
+        <v>90</v>
       </c>
       <c r="M6" t="n">
-        <v>48.57142857142857</v>
+        <v>72.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>COMPRA MODERADA</t>
         </is>
       </c>
     </row>
@@ -751,92 +751,716 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2069384299168635</v>
+        <v>0.2069382818126475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8486515303908404</v>
+        <v>0.8539868899481324</v>
       </c>
       <c r="D7" t="n">
-        <v>1887961595.389339</v>
+        <v>1965097203.315662</v>
       </c>
       <c r="E7" t="n">
-        <v>7.872273842718261e-12</v>
+        <v>7.324846663579629e-12</v>
       </c>
       <c r="F7" t="n">
-        <v>64.28571428571428</v>
+        <v>92.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2900828473447833</v>
+        <v>0.2750544998927322</v>
       </c>
       <c r="H7" t="n">
         <v>0.2320005356687789</v>
       </c>
       <c r="I7" t="n">
-        <v>42.85714285714285</v>
+        <v>30</v>
       </c>
       <c r="J7" t="n">
-        <v>28.57142857142857</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>64.28571428571428</v>
+        <v>92.5</v>
       </c>
       <c r="L7" t="n">
-        <v>57.14285714285715</v>
+        <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>47.85714285714285</v>
+        <v>62.75</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>COMPRA MODERADA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3891567935315539</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.415164917480249</v>
+      </c>
+      <c r="D8" t="n">
+        <v>305083982.0285343</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.59382968532927e-11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2658475260538358</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2356576570050664</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L8" t="n">
+        <v>85</v>
+      </c>
+      <c r="M8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>COMPRA MODERADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BPAC11</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8723906410050846</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.795473343298629</v>
+      </c>
+      <c r="D9" t="n">
+        <v>672211787.9171462</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.780498149560649e-11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3798624807423003</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2996979632178868</v>
+      </c>
+      <c r="I9" t="n">
+        <v>70</v>
+      </c>
+      <c r="J9" t="n">
+        <v>75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30</v>
+      </c>
+      <c r="M9" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4351572005999469</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.178088442065718</v>
+      </c>
+      <c r="D10" t="n">
+        <v>214630220.641554</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7.118133994725355e-11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2731148877027023</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2950370246786932</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>54</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>B3SA3</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B11" t="n">
         <v>0.5652946993579147</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.603692759145953</v>
-      </c>
-      <c r="D8" t="n">
-        <v>718105518.3993748</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.979485253428927e-11</v>
-      </c>
-      <c r="F8" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.391607290155775</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3268833044944129</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="C11" t="n">
+        <v>1.60636460538609</v>
+      </c>
+      <c r="D11" t="n">
+        <v>735689106.6381091</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.648841306177606e-11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3848047824991799</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.326883304494413</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
+        <v>70</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CMIG4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2073366268588333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9178408322187571</v>
+      </c>
+      <c r="D12" t="n">
+        <v>140328841.298512</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.300003725718047e-11</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2730079963293071</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2159653738419742</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K12" t="n">
+        <v>35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1835250164673701</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6735150016737629</v>
+      </c>
+      <c r="D13" t="n">
+        <v>548551949.2075239</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.897843747357004e-11</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3043585734769</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2480749195310926</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>60</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3173569035095156</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.294946776151718</v>
+      </c>
+      <c r="D14" t="n">
+        <v>63415354.03135391</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.300490102629428e-10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2861116741962522</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2282730427211578</v>
+      </c>
+      <c r="I14" t="n">
+        <v>35</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>65</v>
+      </c>
+      <c r="M14" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4734836304930192</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.716616986122147</v>
+      </c>
+      <c r="D15" t="n">
+        <v>155228925.9065719</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.665831753078481e-10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4669745848596029</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3275497332138042</v>
+      </c>
+      <c r="I15" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" t="n">
+        <v>70</v>
+      </c>
+      <c r="K15" t="n">
+        <v>35</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>43</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.657440006545143</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.40992991951932</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31126376.16107577</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.590553192987411e-10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.562923499652882</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4015815611518613</v>
+      </c>
+      <c r="I16" t="n">
+        <v>95</v>
+      </c>
+      <c r="J16" t="n">
         <v>100</v>
       </c>
-      <c r="J8" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NEUTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.05259838402796235</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.1793372011702252</v>
+      </c>
+      <c r="D17" t="n">
+        <v>945156962.9523141</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.878604030643424e-11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3383418151527141</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3109067758927472</v>
+      </c>
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>80</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3440992444295181</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7767610250646355</v>
+      </c>
+      <c r="D18" t="n">
+        <v>92180799.61228144</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.956183780587861e-10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3313297017178391</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.335042310596612</v>
+      </c>
+      <c r="I18" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="n">
+        <v>44.99999999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.4455812064768776</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7190918507700694</v>
+      </c>
+      <c r="D19" t="n">
+        <v>185846133.9653197</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.710234443284166e-10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6594759159479772</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5047893061829969</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>35</v>
+      </c>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>21.42857142857143</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>EVITAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.2035293579101562</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4320579438463107</v>
+      </c>
+      <c r="D20" t="n">
+        <v>123911418.4472425</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.947787954523034e-10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.525996820518986</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3997199290124713</v>
+      </c>
+      <c r="I20" t="n">
+        <v>90</v>
+      </c>
+      <c r="J20" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>VENDA FORTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AZZA3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.08771372351520745</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1769720545322384</v>
+      </c>
+      <c r="D21" t="n">
+        <v>74300549.18361846</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.552598163620268e-10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3897914426792795</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3599359751696338</v>
+      </c>
+      <c r="I21" t="n">
+        <v>80</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>VENDA FORTE</t>
         </is>
       </c>
     </row>
@@ -851,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,92 +1498,261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9977540622750996</v>
+        <v>1.657440006545143</v>
       </c>
       <c r="C2" t="n">
-        <v>3.524412195831653</v>
+        <v>4.40992991951932</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8207620043812851</v>
+        <v>0.9977540622750996</v>
       </c>
       <c r="C3" t="n">
-        <v>3.326412780089652</v>
+        <v>3.523123972571357</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6897098437509033</v>
+        <v>0.7674675202273207</v>
       </c>
       <c r="C4" t="n">
-        <v>3.147924644483759</v>
+        <v>3.430425306946491</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3611223549013032</v>
+        <v>0.8207620043812851</v>
       </c>
       <c r="C5" t="n">
-        <v>1.694658525640141</v>
+        <v>3.315576634856987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B3SA3</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5652946993579147</v>
+        <v>0.6897098437509033</v>
       </c>
       <c r="C6" t="n">
-        <v>1.603692759145953</v>
+        <v>3.142741731706303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2069384299168635</v>
+        <v>0.8723906410050846</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8486515303908404</v>
+        <v>2.795473343298629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.002795726117860386</v>
+        <v>0.4734836304930192</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01056761352176577</v>
+        <v>1.716616986122147</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3611223549013032</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.69311549253637</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5652946993579147</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.60636460538609</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3891567935315539</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.415164917480249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3173569035095156</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.294946776151718</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4351572005999469</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.178088442065718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CMIG4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2073366268588333</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9178408322187571</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2069382818126475</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8539868899481324</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3440992444295181</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7767610250646355</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4455812064768776</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7190918507700694</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.1835250164673701</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6735150016737629</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.2035293579101562</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4320579438463107</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AZZA3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.08771372351520745</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1769720545322384</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.05259838402796235</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.1793372011702252</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,65 +1794,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14768618124.3547</v>
+        <v>2462520192.389824</v>
       </c>
       <c r="C2" t="n">
-        <v>7.794816665266045e-13</v>
+        <v>7.219603890928269e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>92.85714285714286</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2398868387.076423</v>
+        <v>1965097203.315662</v>
       </c>
       <c r="C3" t="n">
-        <v>7.647041598128165e-12</v>
+        <v>7.324846663579629e-12</v>
       </c>
       <c r="D3" t="n">
-        <v>78.57142857142857</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1887961595.389339</v>
+        <v>1720748464.992015</v>
       </c>
       <c r="C4" t="n">
-        <v>7.872273842718261e-12</v>
+        <v>9.931335673099017e-12</v>
       </c>
       <c r="D4" t="n">
-        <v>64.28571428571428</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1686611723.969523</v>
+        <v>945156962.9523141</v>
       </c>
       <c r="C5" t="n">
-        <v>1.00673188090829e-11</v>
+        <v>1.878604030643424e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1069,45 +1862,253 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>912551371.7137746</v>
+        <v>936702989.6828333</v>
       </c>
       <c r="C6" t="n">
-        <v>1.777495030877855e-11</v>
+        <v>1.602628234031397e-11</v>
       </c>
       <c r="D6" t="n">
-        <v>35.71428571428571</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>B3SA3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>444647890.4039565</v>
+        <v>735689106.6381091</v>
       </c>
       <c r="C7" t="n">
-        <v>2.519363398876523e-11</v>
+        <v>2.648841306177606e-11</v>
       </c>
       <c r="D7" t="n">
-        <v>14.28571428571429</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B3SA3</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>718105518.3993748</v>
+        <v>451478543.6449369</v>
       </c>
       <c r="C8" t="n">
-        <v>2.979485253428927e-11</v>
+        <v>2.610922385939225e-11</v>
       </c>
       <c r="D8" t="n">
-        <v>14.28571428571428</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BPAC11</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>672211787.9171462</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.780498149560649e-11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>548551949.2075239</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.897843747357004e-11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GGBR4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>305083982.0285343</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.59382968532927e-11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>214630220.641554</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.118133994725355e-11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>185846133.9653197</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.710234443284166e-10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>155228925.9065719</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.665831753078481e-10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CMIG4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>140328841.298512</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9.300003725718047e-11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEOE3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>55593558.19838388</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.730831357123434e-11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>123911418.4472425</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.947787954523034e-10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>92180799.61228144</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.956183780587861e-10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AZZA3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>74300549.18361846</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.552598163620268e-10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>63415354.03135391</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.300490102629428e-10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31126376.16107577</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7.590553192987411e-10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,17 +2150,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2541466886367213</v>
+        <v>0.01860445309896535</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2151546327929952</v>
+        <v>0.02885617245514972</v>
       </c>
       <c r="D2" t="n">
-        <v>14.28571428571428</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1169,92 +2170,300 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.260145169409522</v>
+        <v>0.2621068729596222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2301036255099778</v>
+        <v>0.2309923257263864</v>
       </c>
       <c r="D3" t="n">
-        <v>28.57142857142857</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2900828473447833</v>
+        <v>0.2658475260538358</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2320005356687789</v>
+        <v>0.2356576570050664</v>
       </c>
       <c r="D4" t="n">
-        <v>42.85714285714285</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3070159486932991</v>
+        <v>0.2730079963293071</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2864134091531322</v>
+        <v>0.2159653738419742</v>
       </c>
       <c r="D5" t="n">
-        <v>57.14285714285714</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3252733872921393</v>
+        <v>0.2731148877027023</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2523599946119469</v>
+        <v>0.2950370246786932</v>
       </c>
       <c r="D6" t="n">
-        <v>71.42857142857143</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3567095385327261</v>
+        <v>0.2750544998927322</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2543366296571614</v>
+        <v>0.2320005356687789</v>
       </c>
       <c r="D7" t="n">
-        <v>85.71428571428571</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2861116741962522</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2282730427211578</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PETR3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3043585734769</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2480749195310926</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BBDC4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3082365131172478</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2864134091531322</v>
+      </c>
+      <c r="D10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3283468072948462</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2524664077859532</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3313297017178391</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.335042310596612</v>
+      </c>
+      <c r="D12" t="n">
+        <v>55.00000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3383418151527141</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3109067758927472</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3639053817002734</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2579701008656878</v>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BPAC11</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3798624807423003</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2996979632178868</v>
+      </c>
+      <c r="D15" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>B3SA3</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.391607290155775</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.3268833044944129</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B16" t="n">
+        <v>0.3848047824991799</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.326883304494413</v>
+      </c>
+      <c r="D16" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AZZA3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3897914426792795</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3599359751696338</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4669745848596029</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.3275497332138042</v>
+      </c>
+      <c r="D18" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.525996820518986</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3997199290124713</v>
+      </c>
+      <c r="D19" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.562923499652882</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4015815611518613</v>
+      </c>
+      <c r="D20" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.6594759159479772</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5047893061829969</v>
+      </c>
+      <c r="D21" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1292,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.98%</t>
+          <t>49.87%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +2513,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R$ 3259.6M</t>
+          <t>R$ 594.0M</t>
         </is>
       </c>
     </row>
@@ -1316,7 +2525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.21%</t>
+          <t>34.99%</t>
         </is>
       </c>
     </row>
@@ -1327,7 +2536,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1338,7 +2547,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-09 20:03</t>
+          <t>2026-03-09 21:20</t>
         </is>
       </c>
     </row>
